--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -362,7 +362,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,13 +386,6 @@
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -851,148 +844,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1505,7 +1498,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11">

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148F2E22-6D93-4E1B-8E16-E9390DD5B8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C98867C-92B0-4EF5-B015-A8018EB269EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="109">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1128,14 +1128,16 @@
       <c r="J6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K6" s="6"/>
+      <c r="K6" s="6">
+        <v>5000001</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>40203</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>77</v>
@@ -1157,7 +1159,9 @@
       <c r="J7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K7" s="6"/>
+      <c r="K7" s="6">
+        <v>55010001</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
@@ -1197,11 +1201,9 @@
         <v>60204</v>
       </c>
       <c r="B9" s="1">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>67</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C9" s="3"/>
       <c r="D9" s="3">
         <v>6</v>
       </c>
@@ -1327,7 +1329,7 @@
         <v>100204</v>
       </c>
       <c r="B13" s="1">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>67</v>
@@ -2287,7 +2289,7 @@
         <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2295,7 +2297,7 @@
         <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C98867C-92B0-4EF5-B015-A8018EB269EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6948AF1A-AE47-463B-84E0-2E0051DA4457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="119">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -480,6 +480,44 @@
   </si>
   <si>
     <t>参数变量id:变化值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒计时结束前，护盾值降低&gt;=&lt;配置值时</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒计时结束前护盾值从&gt;1降低为配置值时</t>
+  </si>
+  <si>
+    <t>倒计时结束前护盾值从&gt;1降低为&lt;=配置值时</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550501:1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560501:0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570501:0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580501:0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600201:0</t>
+  </si>
+  <si>
+    <t>3600701:0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600401:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1091,7 +1129,7 @@
         <v>12</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K5" s="6">
         <v>8</v>
@@ -1190,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K8" s="6">
         <v>8</v>
@@ -1252,7 +1290,7 @@
         <v>12</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K10" s="6">
         <v>8</v>
@@ -1318,7 +1356,7 @@
         <v>12</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K12" s="6">
         <v>8</v>
@@ -1512,7 +1550,7 @@
         <v>12</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="K18" s="6">
         <v>8</v>
@@ -1545,7 +1583,7 @@
         <v>12</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K19" s="6">
         <v>8</v>
@@ -1642,7 +1680,7 @@
         <v>12</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K22" s="6">
         <v>8</v>
@@ -1777,6 +1815,32 @@
       </c>
     </row>
     <row r="27" spans="1:12">
+      <c r="B27" s="1">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="3">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="2">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
       <c r="L27" s="2"/>
     </row>
   </sheetData>
@@ -2096,7 +2160,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21444FDA-7D11-468F-8B6C-690382C676F1}">
-  <dimension ref="A5:F23"/>
+  <dimension ref="A5:F27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -2156,6 +2220,7 @@
       <c r="A9" s="1">
         <v>5</v>
       </c>
+      <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
         <v>93</v>
       </c>
@@ -2230,6 +2295,7 @@
       <c r="A14" s="1">
         <v>11</v>
       </c>
+      <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
@@ -2238,6 +2304,7 @@
       <c r="A15" s="1">
         <v>12</v>
       </c>
+      <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
         <v>72</v>
       </c>
@@ -2255,6 +2322,7 @@
       <c r="A17" s="1">
         <v>14</v>
       </c>
+      <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
@@ -2268,35 +2336,43 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1">
+    <row r="19" spans="1:3">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
         <v>101</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1">
+    <row r="25" spans="1:3">
+      <c r="A25" s="1">
         <v>102</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B25" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1">
+    <row r="26" spans="1:3">
+      <c r="A26" s="1">
         <v>103</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B26" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1">
+    <row r="27" spans="1:3">
+      <c r="A27" s="1">
         <v>104</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>103</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6948AF1A-AE47-463B-84E0-2E0051DA4457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAD1424-8B73-4D7C-8E2F-7ECEE650C1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="备注类型枚举" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_auto_condition_v8!$A$4:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_auto_condition_v8!$A$4:$K$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -494,30 +494,31 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>3550501:1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560501:0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570501:0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580501:0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600201:0</t>
-  </si>
-  <si>
-    <t>3600701:0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600401:0</t>
+    <t>3550501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580501:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600401:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600201:2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1550,7 +1551,7 @@
         <v>12</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K18" s="6">
         <v>8</v>
@@ -1680,7 +1681,7 @@
         <v>12</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K22" s="6">
         <v>8</v>
@@ -1844,7 +1845,7 @@
       <c r="L27" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K26" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}"/>
+  <autoFilter ref="A4:K27" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAD1424-8B73-4D7C-8E2F-7ECEE650C1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A45377-2183-4D0D-A87A-3410D2DE65C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -428,10 +428,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>累计攻击&gt;=次数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>value_variable</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -519,6 +515,10 @@
   </si>
   <si>
     <t>3600201:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计普通攻击&gt;=次数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1001,7 +1001,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
@@ -1022,13 +1022,13 @@
         <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1057,13 +1057,13 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1095,7 +1095,7 @@
         <v>92</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>80</v>
@@ -1130,7 +1130,7 @@
         <v>12</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K5" s="6">
         <v>8</v>
@@ -1229,7 +1229,7 @@
         <v>12</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K8" s="6">
         <v>8</v>
@@ -1291,7 +1291,7 @@
         <v>12</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K10" s="6">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K12" s="6">
         <v>8</v>
@@ -1551,7 +1551,7 @@
         <v>12</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K18" s="6">
         <v>8</v>
@@ -1584,7 +1584,7 @@
         <v>12</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K19" s="6">
         <v>8</v>
@@ -1681,7 +1681,7 @@
         <v>12</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K22" s="6">
         <v>8</v>
@@ -1704,10 +1704,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="2">
@@ -1820,7 +1820,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D27" s="3">
         <v>25</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="2">
@@ -2174,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1"/>
     </row>
@@ -2342,7 +2342,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2350,7 +2350,7 @@
         <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2358,7 +2358,7 @@
         <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2366,7 +2366,7 @@
         <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2374,7 +2374,7 @@
         <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A45377-2183-4D0D-A87A-3410D2DE65C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27568894-6954-4820-B1A7-FEDE996DB760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="备注类型枚举" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_auto_condition_v8!$A$4:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_auto_condition_v8!$A$4:$K$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -81,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -294,9 +292,6 @@
     <t>释放旋风斩</t>
   </si>
   <si>
-    <t>固定时间释放</t>
-  </si>
-  <si>
     <t>攻击暴击</t>
   </si>
   <si>
@@ -400,10 +395,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>累计攻击次数&gt;=8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>自身生命值&gt;=&lt;最大生命值百万分比</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -519,6 +510,28 @@
   </si>
   <si>
     <t>累计普通攻击&gt;=次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标有冰冻状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标冰冻时—触发释放—伤害</t>
+  </si>
+  <si>
+    <t>使冰冻的目标再次冰冻时—触发释放—伤害</t>
+  </si>
+  <si>
+    <t>目标有燃烧状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>正义光环效果层数&gt;=1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计攻击次数&gt;=12</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -973,35 +986,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="52.625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
@@ -1022,16 +1034,16 @@
         <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="K2" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1042,11 +1054,11 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="F3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1057,18 +1069,18 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>51</v>
@@ -1077,39 +1089,39 @@
         <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
+        <v>1010001</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1">
-        <v>10101</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1121,30 +1133,30 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I5" s="2">
         <v>12</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K5" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
-        <v>20102</v>
+        <v>2010002</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -1159,7 +1171,7 @@
         <v>53</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2">
         <v>12</v>
@@ -1171,23 +1183,25 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
-        <v>40203</v>
+        <v>3010001</v>
       </c>
       <c r="B7" s="1">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="G7" s="3" t="s">
         <v>54</v>
       </c>
@@ -1202,56 +1216,58 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
-        <v>50101</v>
+        <v>4010003</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="2">
         <v>12</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>55010001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
-        <v>60204</v>
+        <v>4020101</v>
       </c>
       <c r="B9" s="1">
-        <v>102</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="D9" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3">
         <v>2</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="2">
@@ -1264,24 +1280,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
-        <v>70101</v>
+        <v>5010001</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>45</v>
@@ -1291,33 +1307,31 @@
         <v>12</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K10" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
-        <v>80106</v>
+        <v>6010102</v>
       </c>
       <c r="B11" s="1">
+        <v>102</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="3">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="3">
-        <v>8</v>
-      </c>
       <c r="E11" s="3">
         <v>1</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="2">
@@ -1330,24 +1344,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
-        <v>90101</v>
+        <v>7010001</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="3">
         <v>1</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>45</v>
@@ -1357,31 +1371,33 @@
         <v>12</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K12" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
-        <v>100204</v>
+        <v>8010006</v>
       </c>
       <c r="B13" s="1">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="G13" s="3" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="2">
@@ -1390,62 +1406,62 @@
       <c r="J13" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
-        <v>110107</v>
+        <v>9010001</v>
       </c>
       <c r="B14" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="2">
         <v>12</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K14" s="6">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
-        <v>120108</v>
+        <v>10020004</v>
       </c>
       <c r="B15" s="1">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="2">
@@ -1454,31 +1470,29 @@
       <c r="J15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K15" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
-        <v>140109</v>
+        <v>11010007</v>
       </c>
       <c r="B16" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" s="3">
         <v>1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="2">
@@ -1488,244 +1502,246 @@
         <v>0</v>
       </c>
       <c r="K16" s="6">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
-        <v>150109</v>
+        <v>12010008</v>
       </c>
       <c r="B17" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D17" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E17" s="3">
         <v>1</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K17" s="6">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
-        <v>170101</v>
+        <v>14010009</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E18" s="3">
         <v>1</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="2">
         <v>12</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
-        <v>180101</v>
+        <v>15010009</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="3">
         <v>1</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>190102</v>
+        <v>17010001</v>
       </c>
       <c r="B20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D20" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3">
         <v>1</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="2">
         <v>12</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K20" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
-        <v>200213</v>
+        <v>18010001</v>
       </c>
       <c r="B21" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D21" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" s="3">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G21" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="2">
         <v>12</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K21" s="6">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
-        <v>210101</v>
+        <v>19010002</v>
       </c>
       <c r="B22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" s="3">
         <v>1</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="2">
         <v>12</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>10010001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
-        <v>230115</v>
+        <v>21010001</v>
       </c>
       <c r="B23" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" s="3">
         <v>1</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="2">
         <v>12</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K23" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
-        <v>230216</v>
+        <v>23010015</v>
       </c>
       <c r="B24" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>75</v>
@@ -1734,103 +1750,108 @@
         <v>23</v>
       </c>
       <c r="E24" s="3">
-        <v>2</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="G24" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K24" s="6">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
-        <v>240114</v>
+        <v>23020016</v>
       </c>
       <c r="B25" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D25" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="3">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>29</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K25" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
-        <v>240216</v>
+        <v>24010014</v>
       </c>
       <c r="B26" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D26" s="3">
         <v>24</v>
       </c>
       <c r="E26" s="3">
-        <v>2</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="G26" s="3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K26" s="6">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>24020016</v>
+      </c>
       <c r="B27" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="2">
@@ -1840,12 +1861,41 @@
         <v>0</v>
       </c>
       <c r="K27" s="6">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>24020017</v>
+      </c>
+      <c r="B28" s="1">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="3">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="2">
+        <v>23</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="L27" s="2"/>
+      <c r="K28" s="6">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K27" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1855,13 +1905,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F74B45-2685-4739-BCB4-4B8546744CDD}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>50</v>
@@ -1871,7 +1921,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1881,7 +1931,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1891,7 +1941,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1901,7 +1951,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1911,7 +1961,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>33</v>
@@ -1919,7 +1969,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1929,7 +1979,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1939,7 +1989,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1949,7 +1999,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1959,7 +2009,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>34</v>
@@ -1967,7 +2017,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1977,7 +2027,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1987,7 +2037,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1997,7 +2047,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -2007,7 +2057,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -2019,7 +2069,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -2031,7 +2081,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -2043,7 +2093,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,7 +2105,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -2067,7 +2117,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -2079,7 +2129,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>47</v>
@@ -2089,7 +2139,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2101,7 +2151,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -2113,7 +2163,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -2127,7 +2177,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -2141,7 +2191,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -2161,78 +2211,78 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21444FDA-7D11-468F-8B6C-690382C676F1}">
-  <dimension ref="A5:F27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A5:F28"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1"/>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1"/>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1">
         <v>7</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2247,12 +2297,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1"/>
       <c r="E11" s="1">
@@ -2262,37 +2312,37 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C12" s="1"/>
       <c r="E12" s="1">
         <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C13" s="1"/>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -2301,25 +2351,25 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2328,53 +2378,61 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27568894-6954-4820-B1A7-FEDE996DB760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CD62EE-4694-47D9-A468-8BBAE86425DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="124">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -532,6 +532,10 @@
   </si>
   <si>
     <t>累计攻击次数&gt;=12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发回血</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -986,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -1893,6 +1897,35 @@
       </c>
       <c r="K28" s="6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>26010001</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="1">
+        <v>26</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CD62EE-4694-47D9-A468-8BBAE86425DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6254769-5EE9-40A7-B075-7B90C21E8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -1919,7 +1919,7 @@
         <v>123</v>
       </c>
       <c r="I29" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6254769-5EE9-40A7-B075-7B90C21E8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27568894-6954-4820-B1A7-FEDE996DB760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -532,10 +532,6 @@
   </si>
   <si>
     <t>累计攻击次数&gt;=12</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发回血</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -990,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -1897,35 +1893,6 @@
       </c>
       <c r="K28" s="6">
         <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A29" s="1">
-        <v>26010001</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="1">
-        <v>26</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I29" s="1">
-        <v>12</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27568894-6954-4820-B1A7-FEDE996DB760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6254769-5EE9-40A7-B075-7B90C21E8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="124">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -532,6 +532,10 @@
   </si>
   <si>
     <t>累计攻击次数&gt;=12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发回血</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -986,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -1893,6 +1897,35 @@
       </c>
       <c r="K28" s="6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>26010001</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="1">
+        <v>26</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I29" s="1">
+        <v>12</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6254769-5EE9-40A7-B075-7B90C21E8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A915E3D5-E6E1-4584-B406-FB9794EF7DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="125">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -536,6 +536,10 @@
   </si>
   <si>
     <t>攻击次数—触发回血</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在用</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -543,7 +547,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,8 +604,15 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -624,6 +635,12 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -643,7 +660,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -654,6 +671,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -1918,6 +1936,9 @@
       <c r="F29" s="3" t="s">
         <v>123</v>
       </c>
+      <c r="G29" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="I29" s="1">
         <v>12</v>
       </c>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A915E3D5-E6E1-4584-B406-FB9794EF7DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A588ED-B83C-4132-8DBD-931F643623E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="129">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -540,6 +540,22 @@
   </si>
   <si>
     <t>在用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发寒霜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发燃烧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发麻痹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发冰冻</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1008,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -1946,6 +1962,110 @@
         <v>0</v>
       </c>
       <c r="K29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>26010002</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I30" s="1">
+        <v>12</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>26010003</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" s="1">
+        <v>12</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>26010004</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I32" s="1">
+        <v>12</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>26010005</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I33" s="1">
+        <v>12</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A588ED-B83C-4132-8DBD-931F643623E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23405CE1-6725-4B8C-8682-1DAA7038A6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="130">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -556,6 +556,10 @@
   </si>
   <si>
     <t>攻击次数—触发冰冻</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>废弃</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -628,7 +632,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -657,6 +661,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -676,7 +686,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -688,6 +698,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -1978,8 +1989,8 @@
       <c r="F30" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>124</v>
+      <c r="G30" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="I30" s="1">
         <v>12</v>
@@ -2004,8 +2015,8 @@
       <c r="F31" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>124</v>
+      <c r="G31" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="I31" s="1">
         <v>12</v>
@@ -2030,8 +2041,8 @@
       <c r="F32" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>124</v>
+      <c r="G32" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="I32" s="1">
         <v>12</v>
@@ -2056,8 +2067,8 @@
       <c r="F33" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>124</v>
+      <c r="G33" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="I33" s="1">
         <v>12</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23405CE1-6725-4B8C-8682-1DAA7038A6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EBD0AC-FC84-49EE-94C4-A3E3694A5907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="131">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -560,6 +560,10 @@
   </si>
   <si>
     <t>废弃</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗中</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1035,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -2078,6 +2082,32 @@
       </c>
       <c r="K33" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>720001</v>
+      </c>
+      <c r="B34" s="1">
+        <v>18</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="1">
+        <v>20001</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I34" s="1">
+        <v>12</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2580,6 +2610,14 @@
         <v>106</v>
       </c>
     </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>101</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EBD0AC-FC84-49EE-94C4-A3E3694A5907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB090274-69A1-46BF-8703-2FD362B62F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="132">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -564,6 +564,10 @@
   </si>
   <si>
     <t>战斗中</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—附加毒爆</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1039,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -2108,6 +2112,35 @@
       </c>
       <c r="K34" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>720011</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="1">
+        <v>20011</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I35" s="1">
+        <v>12</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB090274-69A1-46BF-8703-2FD362B62F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8664BBC6-1CB8-4CC4-BE92-59CB13599171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="139">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -569,6 +569,29 @@
   <si>
     <t>攻击次数—附加毒爆</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放动作技能指定id次数</t>
+  </si>
+  <si>
+    <t>爆炎冲刺追加升龙击</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放动作技能指定id1次</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放动作技能指定id2次</t>
+  </si>
+  <si>
+    <t>释放动作技能指定id3次</t>
+  </si>
+  <si>
+    <t>释放动作技能指定id4次</t>
+  </si>
+  <si>
+    <t>释放动作技能指定id5次</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -2141,6 +2164,35 @@
       </c>
       <c r="K35" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>720022</v>
+      </c>
+      <c r="B36" s="1">
+        <v>19</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="1">
+        <v>20022</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>20021</v>
       </c>
     </row>
   </sheetData>
@@ -2459,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21444FDA-7D11-468F-8B6C-690382C676F1}">
-  <dimension ref="A5:F28"/>
+  <dimension ref="A5:F32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -2651,49 +2703,89 @@
         <v>130</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>101</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>102</v>
-      </c>
-      <c r="B25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>103</v>
-      </c>
-      <c r="B26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>104</v>
-      </c>
-      <c r="B27" t="s">
-        <v>100</v>
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>104</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>105</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B32" t="s">
         <v>121</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F32">
-    <sortCondition ref="E5:E32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F36">
+    <sortCondition ref="E5:E36"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8664BBC6-1CB8-4CC4-BE92-59CB13599171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933BB5E8-1FA6-49BA-BA7C-B04597890F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="140">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -571,9 +571,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>释放动作技能指定id次数</t>
-  </si>
-  <si>
     <t>爆炎冲刺追加升龙击</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -592,6 +589,14 @@
   </si>
   <si>
     <t>释放动作技能指定id5次</t>
+  </si>
+  <si>
+    <t>释放动作技能指定id3次</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺3次追加砸地</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1066,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -2174,13 +2179,13 @@
         <v>19</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" s="1">
         <v>20022</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>124</v>
@@ -2192,6 +2197,35 @@
         <v>0</v>
       </c>
       <c r="K36" s="1">
+        <v>20021</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>720023</v>
+      </c>
+      <c r="B37" s="1">
+        <v>21</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="1">
+        <v>20023</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
         <v>20021</v>
       </c>
     </row>
@@ -2708,7 +2742,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2716,7 +2750,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2724,7 +2758,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2732,7 +2766,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2740,7 +2774,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933BB5E8-1FA6-49BA-BA7C-B04597890F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEB18F9-C566-4665-A963-4F9054AB2860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -1999,8 +1999,8 @@
       <c r="F29" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>124</v>
+      <c r="G29" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="I29" s="1">
         <v>12</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEB18F9-C566-4665-A963-4F9054AB2860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D6B27A-F8CE-4D0E-ACCC-45783256A512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="141">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -596,6 +596,10 @@
   </si>
   <si>
     <t>爆炎冲刺3次追加砸地</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发超强电刃</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1071,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -2227,6 +2231,87 @@
       </c>
       <c r="K37" s="1">
         <v>20021</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A38" s="1">
+        <v>720053</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="1">
+        <v>20053</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I38" s="1">
+        <v>12</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A39" s="1">
+        <v>720032</v>
+      </c>
+      <c r="B39" s="1">
+        <v>18</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="1">
+        <v>20032</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I39" s="1">
+        <v>12</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A40" s="1">
+        <v>720033</v>
+      </c>
+      <c r="B40" s="1">
+        <v>18</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="1">
+        <v>20033</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I40" s="1">
+        <v>12</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D6B27A-F8CE-4D0E-ACCC-45783256A512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1291632F-204B-415B-BB9A-EEE5C03B0954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="144">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -600,6 +600,18 @@
   </si>
   <si>
     <t>攻击次数—触发超强电刃</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻概率触发&gt;=（万分比）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻概率触发</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻概率触发电波</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1075,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -2312,6 +2324,35 @@
       </c>
       <c r="K40" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
+        <v>720052</v>
+      </c>
+      <c r="B41" s="1">
+        <v>24</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" s="1">
+        <v>20052</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I41" s="1">
+        <v>12</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>3500</v>
       </c>
     </row>
   </sheetData>
@@ -2862,6 +2903,14 @@
         <v>137</v>
       </c>
     </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>101</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1291632F-204B-415B-BB9A-EEE5C03B0954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A49B9C-E62C-47B5-9226-8A22647A5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="145">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -612,6 +612,10 @@
   </si>
   <si>
     <t>普攻概率触发电波</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>72005201:1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2349,7 +2353,7 @@
         <v>12</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="K41" s="1">
         <v>3500</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A49B9C-E62C-47B5-9226-8A22647A5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F15F49-56CD-4AE6-919C-B5762BBCBD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4992ADC8-F8DB-42F8-95AF-F06E82EA4C43}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="147">
   <si>
     <t>0:0</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -616,6 +616,14 @@
   </si>
   <si>
     <t>72005201:1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试技能</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—附加电弧</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -623,7 +631,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -687,6 +695,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -742,7 +757,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -755,6 +770,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -1091,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11522F-A12D-4D27-A624-9F867539B722}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" bestFit="1" customWidth="1"/>
@@ -2178,8 +2194,8 @@
       <c r="F35" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>124</v>
+      <c r="G35" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="I35" s="1">
         <v>12</v>
@@ -2207,8 +2223,8 @@
       <c r="F36" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>124</v>
+      <c r="G36" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="I36" s="1">
         <v>2</v>
@@ -2236,8 +2252,8 @@
       <c r="F37" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>124</v>
+      <c r="G37" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="I37" s="1">
         <v>2</v>
@@ -2332,19 +2348,19 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>720052</v>
+        <v>720051</v>
       </c>
       <c r="B41" s="1">
-        <v>24</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>142</v>
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D41" s="1">
-        <v>20052</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>143</v>
+        <v>20051</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>124</v>
@@ -2353,9 +2369,38 @@
         <v>12</v>
       </c>
       <c r="J41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A42" s="1">
+        <v>720052</v>
+      </c>
+      <c r="B42" s="1">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="1">
+        <v>20052</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I42" s="1">
+        <v>12</v>
+      </c>
+      <c r="J42" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K42" s="1">
         <v>3500</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -479,7 +479,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,13 +515,6 @@
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -992,148 +985,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2673,7 +2666,7 @@
         <v>31</v>
       </c>
       <c r="K38" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:11">

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -2776,7 +2776,7 @@
         <v>99</v>
       </c>
       <c r="K42" s="1">
-        <v>3500</v>
+        <v>2500</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D29FE4-4BCA-44CD-BDCA-CDE78F8DF74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,18 +36,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pe</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1&gt;
@@ -56,6 +61,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -68,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="133">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -472,14 +478,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,180 +491,65 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,7 +558,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,186 +582,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -884,256 +595,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1141,64 +616,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="适中" xfId="2" builtinId="28"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1476,14 +909,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
@@ -1499,12 +932,12 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1574,7 +1007,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1609,7 +1042,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1010001</v>
       </c>
@@ -1644,7 +1077,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2010002</v>
       </c>
@@ -1679,7 +1112,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3010001</v>
       </c>
@@ -1712,7 +1145,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4010003</v>
       </c>
@@ -1745,7 +1178,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>4020101</v>
       </c>
@@ -1776,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>5010001</v>
       </c>
@@ -1809,7 +1242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>6010102</v>
       </c>
@@ -1840,7 +1273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>7010001</v>
       </c>
@@ -1873,7 +1306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>8010006</v>
       </c>
@@ -1906,7 +1339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>9010001</v>
       </c>
@@ -1939,7 +1372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>10020004</v>
       </c>
@@ -1968,7 +1401,7 @@
       </c>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>11010007</v>
       </c>
@@ -2001,7 +1434,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>12010008</v>
       </c>
@@ -2034,7 +1467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14010009</v>
       </c>
@@ -2067,7 +1500,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15010009</v>
       </c>
@@ -2100,7 +1533,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>17010001</v>
       </c>
@@ -2133,7 +1566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>18010001</v>
       </c>
@@ -2166,7 +1599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>19010002</v>
       </c>
@@ -2199,7 +1632,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21010001</v>
       </c>
@@ -2232,7 +1665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>23010015</v>
       </c>
@@ -2265,7 +1698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23020016</v>
       </c>
@@ -2296,7 +1729,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24010014</v>
       </c>
@@ -2329,7 +1762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>24020016</v>
       </c>
@@ -2360,7 +1793,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24020017</v>
       </c>
@@ -2391,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>26010001</v>
       </c>
@@ -2423,7 +1856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26010002</v>
       </c>
@@ -2449,7 +1882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>26010003</v>
       </c>
@@ -2475,7 +1908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>26010004</v>
       </c>
@@ -2501,7 +1934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>26010005</v>
       </c>
@@ -2527,7 +1960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>720001</v>
       </c>
@@ -2553,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>720011</v>
       </c>
@@ -2582,7 +2015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>720022</v>
       </c>
@@ -2611,7 +2044,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>720023</v>
       </c>
@@ -2640,7 +2073,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>720053</v>
       </c>
@@ -2669,7 +2102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>720032</v>
       </c>
@@ -2695,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>720033</v>
       </c>
@@ -2721,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>720051</v>
       </c>
@@ -2750,7 +2183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>720052</v>
       </c>
@@ -2779,24 +2212,49 @@
         <v>2500</v>
       </c>
     </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A43" s="1">
+        <v>720081</v>
+      </c>
+      <c r="B43" s="1">
+        <v>18</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="1">
+        <v>20081</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I43" s="1">
+        <v>12</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -2806,7 +2264,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2816,7 +2274,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -2826,7 +2284,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -2836,7 +2294,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>101</v>
       </c>
@@ -2846,7 +2304,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -2854,7 +2312,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -2864,7 +2322,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
@@ -2874,7 +2332,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -2884,7 +2342,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>103</v>
       </c>
@@ -2894,7 +2352,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -2902,7 +2360,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>52</v>
       </c>
@@ -2912,7 +2370,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -2922,7 +2380,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>104</v>
       </c>
@@ -2932,7 +2390,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -2942,7 +2400,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,7 +2412,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>105</v>
       </c>
@@ -2966,7 +2424,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -2978,7 +2436,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -2990,7 +2448,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>66</v>
       </c>
@@ -3002,7 +2460,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>107</v>
       </c>
@@ -3014,7 +2472,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>109</v>
@@ -3024,7 +2482,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -3036,7 +2494,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>110</v>
       </c>
@@ -3048,7 +2506,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
@@ -3062,7 +2520,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
@@ -3076,7 +2534,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>114</v>
       </c>
@@ -3089,23 +2547,22 @@
       <c r="F27" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A5:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3114,7 +2571,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -3123,7 +2580,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3138,7 +2595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3153,7 +2610,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3168,7 +2625,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3183,7 +2640,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3198,7 +2655,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3213,7 +2670,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3228,7 +2685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3237,7 +2694,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3246,7 +2703,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3255,7 +2712,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3264,7 +2721,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3273,7 +2730,7 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3281,7 +2738,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3289,7 +2746,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3297,7 +2754,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3305,7 +2762,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3313,7 +2770,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3321,7 +2778,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3329,7 +2786,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3337,7 +2794,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>101</v>
       </c>
@@ -3345,7 +2802,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>102</v>
       </c>
@@ -3353,7 +2810,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>103</v>
       </c>
@@ -3361,7 +2818,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>104</v>
       </c>
@@ -3369,7 +2826,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>105</v>
       </c>
@@ -3378,10 +2835,10 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="E5:F36">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F36">
     <sortCondition ref="E5:E36"/>
   </sortState>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D29FE4-4BCA-44CD-BDCA-CDE78F8DF74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEACC9C-9A07-4047-802D-496C463D7C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -473,6 +473,10 @@
   </si>
   <si>
     <t>正义光环效果层数&gt;=1</t>
+  </si>
+  <si>
+    <t>攻击次数—附加碎冰</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -915,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
@@ -2236,6 +2240,35 @@
       </c>
       <c r="K43" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A44" s="1">
+        <v>720084</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="1">
+        <v>20084</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I44" s="1">
+        <v>12</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEACC9C-9A07-4047-802D-496C463D7C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -29,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,19 +32,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pe</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1&gt;
@@ -61,7 +56,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -376,6 +370,9 @@
     <t>72005201:1</t>
   </si>
   <si>
+    <t>攻击次数—附加碎冰</t>
+  </si>
+  <si>
     <t>条件</t>
   </si>
   <si>
@@ -473,17 +470,19 @@
   </si>
   <si>
     <t>正义光环效果层数&gt;=1</t>
-  </si>
-  <si>
-    <t>攻击次数—附加碎冰</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,65 +494,180 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -562,7 +676,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,12 +700,186 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -599,20 +887,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -620,22 +1144,64 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="差" xfId="1" builtinId="27"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="适中" xfId="2" builtinId="28"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -913,14 +1479,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
@@ -936,12 +1502,12 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -976,7 +1542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1011,7 +1577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1046,7 +1612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>1010001</v>
       </c>
@@ -1081,7 +1647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>2010002</v>
       </c>
@@ -1116,7 +1682,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>3010001</v>
       </c>
@@ -1149,7 +1715,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <v>4010003</v>
       </c>
@@ -1182,7 +1748,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11">
       <c r="A9" s="1">
         <v>4020101</v>
       </c>
@@ -1213,7 +1779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11">
       <c r="A10" s="1">
         <v>5010001</v>
       </c>
@@ -1246,7 +1812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11">
       <c r="A11" s="1">
         <v>6010102</v>
       </c>
@@ -1277,7 +1843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11">
       <c r="A12" s="1">
         <v>7010001</v>
       </c>
@@ -1310,7 +1876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
         <v>8010006</v>
       </c>
@@ -1343,7 +1909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11">
       <c r="A14" s="1">
         <v>9010001</v>
       </c>
@@ -1376,7 +1942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11">
       <c r="A15" s="1">
         <v>10020004</v>
       </c>
@@ -1405,7 +1971,7 @@
       </c>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11">
       <c r="A16" s="1">
         <v>11010007</v>
       </c>
@@ -1438,7 +2004,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:11">
       <c r="A17" s="1">
         <v>12010008</v>
       </c>
@@ -1471,7 +2037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:11">
       <c r="A18" s="1">
         <v>14010009</v>
       </c>
@@ -1504,7 +2070,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11">
       <c r="A19" s="1">
         <v>15010009</v>
       </c>
@@ -1537,7 +2103,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:11">
       <c r="A20" s="1">
         <v>17010001</v>
       </c>
@@ -1570,7 +2136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:11">
       <c r="A21" s="1">
         <v>18010001</v>
       </c>
@@ -1603,7 +2169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:11">
       <c r="A22" s="1">
         <v>19010002</v>
       </c>
@@ -1636,7 +2202,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11">
       <c r="A23" s="1">
         <v>21010001</v>
       </c>
@@ -1669,7 +2235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:11">
       <c r="A24" s="1">
         <v>23010015</v>
       </c>
@@ -1702,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:11">
       <c r="A25" s="1">
         <v>23020016</v>
       </c>
@@ -1733,7 +2299,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:11">
       <c r="A26" s="1">
         <v>24010014</v>
       </c>
@@ -1766,7 +2332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:11">
       <c r="A27" s="1">
         <v>24020016</v>
       </c>
@@ -1797,7 +2363,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:11">
       <c r="A28" s="1">
         <v>24020017</v>
       </c>
@@ -1828,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:11">
       <c r="A29" s="1">
         <v>26010001</v>
       </c>
@@ -1860,7 +2426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:11">
       <c r="A30" s="1">
         <v>26010002</v>
       </c>
@@ -1886,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:11">
       <c r="A31" s="1">
         <v>26010003</v>
       </c>
@@ -1912,7 +2478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11">
       <c r="A32" s="1">
         <v>26010004</v>
       </c>
@@ -1938,7 +2504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>26010005</v>
       </c>
@@ -1964,7 +2530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>720001</v>
       </c>
@@ -1990,7 +2556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>720011</v>
       </c>
@@ -2019,7 +2585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:11">
       <c r="A36" s="1">
         <v>720022</v>
       </c>
@@ -2048,7 +2614,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11">
       <c r="A37" s="1">
         <v>720023</v>
       </c>
@@ -2077,7 +2643,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:11">
       <c r="A38" s="1">
         <v>720053</v>
       </c>
@@ -2103,10 +2669,10 @@
         <v>31</v>
       </c>
       <c r="K38" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="1">
         <v>720032</v>
       </c>
@@ -2132,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:11">
       <c r="A40" s="1">
         <v>720033</v>
       </c>
@@ -2158,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:11">
       <c r="A41" s="1">
         <v>720051</v>
       </c>
@@ -2187,7 +2753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:11">
       <c r="A42" s="1">
         <v>720052</v>
       </c>
@@ -2216,7 +2782,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:11">
       <c r="A43" s="1">
         <v>720081</v>
       </c>
@@ -2242,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:11">
       <c r="A44" s="1">
         <v>720084</v>
       </c>
@@ -2256,7 +2822,7 @@
         <v>20084</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>88</v>
@@ -2272,32 +2838,33 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2307,7 +2874,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -2317,7 +2884,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -2327,17 +2894,17 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -2345,7 +2912,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -2355,7 +2922,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
@@ -2365,7 +2932,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -2375,17 +2942,17 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -2393,7 +2960,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>52</v>
       </c>
@@ -2403,7 +2970,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -2413,17 +2980,17 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,7 +3000,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -2445,19 +3012,19 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -2469,7 +3036,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -2481,7 +3048,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>66</v>
       </c>
@@ -2493,29 +3060,29 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -2527,9 +3094,9 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -2539,12 +3106,12 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>70</v>
@@ -2553,12 +3120,12 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>77</v>
@@ -2567,53 +3134,54 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A5:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2628,7 +3196,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2643,13 +3211,13 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E9" s="1">
         <v>7</v>
@@ -2658,7 +3226,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2673,7 +3241,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2685,30 +3253,30 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1"/>
       <c r="E12" s="1">
         <v>8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1"/>
       <c r="E13" s="1">
@@ -2718,34 +3286,34 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2754,24 +3322,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2779,7 +3347,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2787,15 +3355,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2803,75 +3371,75 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="1">
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="1">
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="1">
         <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="1">
         <v>104</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="1">
         <v>105</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F36">
+  <sortState ref="E5:F36">
     <sortCondition ref="E5:E36"/>
   </sortState>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517CCC67-F378-4823-A17F-68918D2AF017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,18 +36,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pe</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1&gt;
@@ -56,6 +61,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -68,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="137">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -470,19 +476,25 @@
   </si>
   <si>
     <t>正义光环效果层数&gt;=1</t>
+  </si>
+  <si>
+    <t>攻击次数—附加火焰溅射</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发火焰冲击</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发引燃</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,180 +506,65 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -676,7 +573,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,186 +597,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -887,256 +610,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1144,64 +631,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="适中" xfId="2" builtinId="28"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1479,14 +924,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
@@ -1502,12 +947,12 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1542,7 +987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1577,7 +1022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,7 +1057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1010001</v>
       </c>
@@ -1647,7 +1092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2010002</v>
       </c>
@@ -1682,7 +1127,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3010001</v>
       </c>
@@ -1715,7 +1160,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4010003</v>
       </c>
@@ -1748,7 +1193,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>4020101</v>
       </c>
@@ -1779,7 +1224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>5010001</v>
       </c>
@@ -1812,7 +1257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>6010102</v>
       </c>
@@ -1843,7 +1288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>7010001</v>
       </c>
@@ -1876,7 +1321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>8010006</v>
       </c>
@@ -1909,7 +1354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>9010001</v>
       </c>
@@ -1942,7 +1387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>10020004</v>
       </c>
@@ -1971,7 +1416,7 @@
       </c>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>11010007</v>
       </c>
@@ -2004,7 +1449,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>12010008</v>
       </c>
@@ -2037,7 +1482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14010009</v>
       </c>
@@ -2070,7 +1515,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15010009</v>
       </c>
@@ -2103,7 +1548,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>17010001</v>
       </c>
@@ -2136,7 +1581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>18010001</v>
       </c>
@@ -2169,7 +1614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>19010002</v>
       </c>
@@ -2202,7 +1647,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21010001</v>
       </c>
@@ -2235,7 +1680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>23010015</v>
       </c>
@@ -2268,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23020016</v>
       </c>
@@ -2299,7 +1744,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24010014</v>
       </c>
@@ -2332,7 +1777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>24020016</v>
       </c>
@@ -2363,7 +1808,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24020017</v>
       </c>
@@ -2394,7 +1839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>26010001</v>
       </c>
@@ -2426,7 +1871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26010002</v>
       </c>
@@ -2452,7 +1897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>26010003</v>
       </c>
@@ -2478,7 +1923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>26010004</v>
       </c>
@@ -2504,7 +1949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>26010005</v>
       </c>
@@ -2530,7 +1975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>720001</v>
       </c>
@@ -2556,7 +2001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>720011</v>
       </c>
@@ -2585,7 +2030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>720022</v>
       </c>
@@ -2614,7 +2059,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>720023</v>
       </c>
@@ -2643,7 +2088,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>720053</v>
       </c>
@@ -2672,7 +2117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>720032</v>
       </c>
@@ -2698,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>720033</v>
       </c>
@@ -2724,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>720051</v>
       </c>
@@ -2753,7 +2198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>720052</v>
       </c>
@@ -2782,7 +2227,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>720081</v>
       </c>
@@ -2808,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>720084</v>
       </c>
@@ -2837,24 +2282,136 @@
         <v>1</v>
       </c>
     </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>720091</v>
+      </c>
+      <c r="B45" s="1">
+        <v>18</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="1">
+        <v>20091</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I45" s="1">
+        <v>12</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>720101</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="1">
+        <v>20101</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I46" s="1">
+        <v>12</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>720102</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="1">
+        <v>20102</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I47" s="1">
+        <v>12</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A48" s="1">
+        <v>720102</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1">
+        <v>20103</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I48" s="1">
+        <v>12</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>101</v>
@@ -2864,7 +2421,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2874,7 +2431,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -2884,7 +2441,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -2894,7 +2451,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>102</v>
       </c>
@@ -2904,7 +2461,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -2912,7 +2469,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -2922,7 +2479,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
@@ -2932,7 +2489,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -2942,7 +2499,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>104</v>
       </c>
@@ -2952,7 +2509,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -2960,7 +2517,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>52</v>
       </c>
@@ -2970,7 +2527,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -2980,7 +2537,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>105</v>
       </c>
@@ -2990,7 +2547,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -3000,7 +2557,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -3012,7 +2569,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>106</v>
       </c>
@@ -3024,7 +2581,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,7 +2593,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -3048,7 +2605,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>66</v>
       </c>
@@ -3060,7 +2617,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>108</v>
       </c>
@@ -3072,7 +2629,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>110</v>
@@ -3082,7 +2639,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -3094,7 +2651,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>111</v>
       </c>
@@ -3106,7 +2663,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>112</v>
       </c>
@@ -3120,7 +2677,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
@@ -3134,7 +2691,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>115</v>
       </c>
@@ -3147,23 +2704,22 @@
       <c r="F27" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A5:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3172,7 +2728,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -3181,7 +2737,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3196,7 +2752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3211,7 +2767,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3226,7 +2782,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3241,7 +2797,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3256,7 +2812,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3271,7 +2827,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3286,7 +2842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3295,7 +2851,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3304,7 +2860,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3313,7 +2869,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3322,7 +2878,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3331,7 +2887,7 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3339,7 +2895,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3347,7 +2903,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3355,7 +2911,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3363,7 +2919,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3371,7 +2927,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3379,7 +2935,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3387,7 +2943,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3395,7 +2951,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>101</v>
       </c>
@@ -3403,7 +2959,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>102</v>
       </c>
@@ -3411,7 +2967,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>103</v>
       </c>
@@ -3419,7 +2975,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>104</v>
       </c>
@@ -3427,7 +2983,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>105</v>
       </c>
@@ -3436,10 +2992,10 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="E5:F36">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F36">
     <sortCondition ref="E5:E36"/>
   </sortState>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517CCC67-F378-4823-A17F-68918D2AF017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D05A9-E44C-40F1-9B44-E968C468F06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="138">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -487,6 +487,10 @@
   </si>
   <si>
     <t>攻击次数—触发引燃</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发毁灭风暴</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -930,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
@@ -2368,7 +2372,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>720102</v>
+        <v>720103</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
@@ -2393,6 +2397,35 @@
       </c>
       <c r="K48" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>720104</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="1">
+        <v>20104</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I49" s="1">
+        <v>12</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D05A9-E44C-40F1-9B44-E968C468F06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27870" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -29,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,19 +32,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pe</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1&gt;
@@ -61,7 +56,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -74,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="138">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -379,6 +373,18 @@
     <t>攻击次数—附加碎冰</t>
   </si>
   <si>
+    <t>攻击次数—附加火焰溅射</t>
+  </si>
+  <si>
+    <t>攻击次数—触发火焰冲击</t>
+  </si>
+  <si>
+    <t>攻击次数—触发引燃</t>
+  </si>
+  <si>
+    <t>攻击次数—触发毁灭风暴</t>
+  </si>
+  <si>
     <t>条件</t>
   </si>
   <si>
@@ -476,29 +482,19 @@
   </si>
   <si>
     <t>正义光环效果层数&gt;=1</t>
-  </si>
-  <si>
-    <t>攻击次数—附加火焰溅射</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发火焰冲击</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发引燃</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发毁灭风暴</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,65 +506,180 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,7 +688,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,12 +712,186 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -614,20 +899,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -635,22 +1156,65 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="差" xfId="1" builtinId="27"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="适中" xfId="2" builtinId="28"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -928,14 +1492,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
@@ -951,12 +1515,12 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -984,14 +1548,14 @@
       <c r="I2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1019,14 +1583,14 @@
       <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="J3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1054,14 +1618,14 @@
       <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>1010001</v>
       </c>
@@ -1089,14 +1653,14 @@
       <c r="I5" s="1">
         <v>12</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="K5" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>2010002</v>
       </c>
@@ -1124,14 +1688,14 @@
       <c r="I6" s="1">
         <v>12</v>
       </c>
-      <c r="J6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="8">
+      <c r="J6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="9">
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>3010001</v>
       </c>
@@ -1157,14 +1721,14 @@
       <c r="I7" s="1">
         <v>12</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="8">
+      <c r="J7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="9">
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <v>4010003</v>
       </c>
@@ -1190,14 +1754,14 @@
       <c r="I8" s="1">
         <v>12</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="8">
+      <c r="J8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="9">
         <v>55010001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11">
       <c r="A9" s="1">
         <v>4020101</v>
       </c>
@@ -1221,14 +1785,14 @@
       <c r="I9" s="1">
         <v>12</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1">
         <v>5010001</v>
       </c>
@@ -1254,14 +1818,14 @@
       <c r="I10" s="1">
         <v>12</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11">
       <c r="A11" s="1">
         <v>6010102</v>
       </c>
@@ -1285,14 +1849,14 @@
       <c r="I11" s="1">
         <v>12</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1">
         <v>7010001</v>
       </c>
@@ -1318,14 +1882,14 @@
       <c r="I12" s="1">
         <v>12</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
         <v>8010006</v>
       </c>
@@ -1351,14 +1915,14 @@
       <c r="I13" s="1">
         <v>12</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="1">
         <v>9010001</v>
       </c>
@@ -1384,14 +1948,14 @@
       <c r="I14" s="1">
         <v>12</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11">
       <c r="A15" s="1">
         <v>10020004</v>
       </c>
@@ -1415,12 +1979,12 @@
       <c r="I15" s="1">
         <v>12</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="1">
         <v>11010007</v>
       </c>
@@ -1446,14 +2010,14 @@
       <c r="I16" s="1">
         <v>12</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" s="8">
+      <c r="J16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="9">
         <v>200000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:11">
       <c r="A17" s="1">
         <v>12010008</v>
       </c>
@@ -1479,14 +2043,14 @@
       <c r="I17" s="1">
         <v>12</v>
       </c>
-      <c r="J17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J17" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1">
         <v>14010009</v>
       </c>
@@ -1512,14 +2076,14 @@
       <c r="I18" s="1">
         <v>12</v>
       </c>
-      <c r="J18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="8">
+      <c r="J18" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="9">
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11">
       <c r="A19" s="1">
         <v>15010009</v>
       </c>
@@ -1545,14 +2109,14 @@
       <c r="I19" s="1">
         <v>23</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="8">
+      <c r="J19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="9">
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:11">
       <c r="A20" s="1">
         <v>17010001</v>
       </c>
@@ -1578,14 +2142,14 @@
       <c r="I20" s="1">
         <v>12</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:11">
       <c r="A21" s="1">
         <v>18010001</v>
       </c>
@@ -1611,14 +2175,14 @@
       <c r="I21" s="1">
         <v>12</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:11">
       <c r="A22" s="1">
         <v>19010002</v>
       </c>
@@ -1644,14 +2208,14 @@
       <c r="I22" s="1">
         <v>12</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="8">
+      <c r="J22" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="9">
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11">
       <c r="A23" s="1">
         <v>21010001</v>
       </c>
@@ -1677,14 +2241,14 @@
       <c r="I23" s="1">
         <v>12</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:11">
       <c r="A24" s="1">
         <v>23010015</v>
       </c>
@@ -1710,14 +2274,14 @@
       <c r="I24" s="1">
         <v>12</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J24" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1">
         <v>23020016</v>
       </c>
@@ -1741,14 +2305,14 @@
       <c r="I25" s="1">
         <v>23</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" s="8">
+      <c r="J25" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="9">
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:11">
       <c r="A26" s="1">
         <v>24010014</v>
       </c>
@@ -1774,14 +2338,14 @@
       <c r="I26" s="1">
         <v>12</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J26" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1">
         <v>24020016</v>
       </c>
@@ -1805,14 +2369,14 @@
       <c r="I27" s="1">
         <v>23</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K27" s="8">
+      <c r="J27" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="9">
         <v>600000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:11">
       <c r="A28" s="1">
         <v>24020017</v>
       </c>
@@ -1836,14 +2400,14 @@
       <c r="I28" s="1">
         <v>23</v>
       </c>
-      <c r="J28" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K28" s="8">
+      <c r="J28" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:11">
       <c r="A29" s="1">
         <v>26010001</v>
       </c>
@@ -1868,14 +2432,14 @@
       <c r="I29" s="1">
         <v>12</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:11">
       <c r="A30" s="1">
         <v>26010002</v>
       </c>
@@ -1894,14 +2458,14 @@
       <c r="I30" s="1">
         <v>12</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:11">
       <c r="A31" s="1">
         <v>26010003</v>
       </c>
@@ -1920,14 +2484,14 @@
       <c r="I31" s="1">
         <v>12</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11">
       <c r="A32" s="1">
         <v>26010004</v>
       </c>
@@ -1946,14 +2510,14 @@
       <c r="I32" s="1">
         <v>12</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>26010005</v>
       </c>
@@ -1972,14 +2536,14 @@
       <c r="I33" s="1">
         <v>12</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>720001</v>
       </c>
@@ -1998,14 +2562,14 @@
       <c r="I34" s="1">
         <v>12</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>720011</v>
       </c>
@@ -2027,14 +2591,14 @@
       <c r="I35" s="1">
         <v>12</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:11">
       <c r="A36" s="1">
         <v>720022</v>
       </c>
@@ -2056,14 +2620,14 @@
       <c r="I36" s="1">
         <v>2</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K36" s="1">
         <v>20021</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11">
       <c r="A37" s="1">
         <v>720023</v>
       </c>
@@ -2085,14 +2649,14 @@
       <c r="I37" s="1">
         <v>2</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="J37" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K37" s="1">
         <v>20021</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:11">
       <c r="A38" s="1">
         <v>720053</v>
       </c>
@@ -2114,14 +2678,14 @@
       <c r="I38" s="1">
         <v>12</v>
       </c>
-      <c r="J38" s="9" t="s">
+      <c r="J38" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K38" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:11">
       <c r="A39" s="1">
         <v>720032</v>
       </c>
@@ -2140,14 +2704,14 @@
       <c r="I39" s="1">
         <v>12</v>
       </c>
-      <c r="J39" s="9" t="s">
+      <c r="J39" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:11">
       <c r="A40" s="1">
         <v>720033</v>
       </c>
@@ -2166,57 +2730,55 @@
       <c r="I40" s="1">
         <v>12</v>
       </c>
-      <c r="J40" s="9" t="s">
+      <c r="J40" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:11">
       <c r="A41" s="1">
-        <v>720051</v>
+        <v>720034</v>
       </c>
       <c r="B41" s="1">
-        <v>1</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="D41" s="1">
-        <v>20051</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>96</v>
-      </c>
+        <v>20102</v>
+      </c>
+      <c r="F41" s="8"/>
       <c r="G41" s="6" t="s">
         <v>88</v>
       </c>
       <c r="I41" s="1">
         <v>12</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="1">
-        <v>720052</v>
+        <v>720051</v>
       </c>
       <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="D42" s="1">
-        <v>20052</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>98</v>
+        <v>20051</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>88</v>
@@ -2224,25 +2786,28 @@
       <c r="I42" s="1">
         <v>12</v>
       </c>
-      <c r="J42" s="9" t="s">
-        <v>99</v>
+      <c r="J42" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="K42" s="1">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="1">
-        <v>720081</v>
+        <v>720052</v>
       </c>
       <c r="B43" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D43" s="1">
-        <v>20081</v>
+        <v>20052</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>88</v>
@@ -2250,28 +2815,25 @@
       <c r="I43" s="1">
         <v>12</v>
       </c>
-      <c r="J43" s="9" t="s">
-        <v>31</v>
+      <c r="J43" s="10" t="s">
+        <v>99</v>
       </c>
       <c r="K43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="1">
-        <v>720084</v>
+        <v>720081</v>
       </c>
       <c r="B44" s="1">
-        <v>1</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="D44" s="1">
-        <v>20084</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>100</v>
+        <v>20081</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>88</v>
@@ -2279,25 +2841,28 @@
       <c r="I44" s="1">
         <v>12</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J44" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="1">
-        <v>720091</v>
+        <v>720084</v>
       </c>
       <c r="B45" s="1">
-        <v>18</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>87</v>
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D45" s="1">
-        <v>20091</v>
+        <v>20084</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>88</v>
@@ -2305,28 +2870,25 @@
       <c r="I45" s="1">
         <v>12</v>
       </c>
-      <c r="J45" s="9" t="s">
+      <c r="J45" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="1">
-        <v>720101</v>
+        <v>720091</v>
       </c>
       <c r="B46" s="1">
-        <v>1</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="D46" s="1">
-        <v>20101</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>134</v>
+        <v>20091</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>88</v>
@@ -2334,28 +2896,28 @@
       <c r="I46" s="1">
         <v>12</v>
       </c>
-      <c r="J46" s="9" t="s">
+      <c r="J46" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="1">
-        <v>720102</v>
+        <v>720101</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="1">
-        <v>20102</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>135</v>
+        <v>20101</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>88</v>
@@ -2363,16 +2925,16 @@
       <c r="I47" s="1">
         <v>12</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:11">
       <c r="A48" s="1">
-        <v>720103</v>
+        <v>720102</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
@@ -2381,10 +2943,10 @@
         <v>24</v>
       </c>
       <c r="D48" s="1">
-        <v>20103</v>
+        <v>20102</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>88</v>
@@ -2392,16 +2954,16 @@
       <c r="I48" s="1">
         <v>12</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="J48" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K48" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11">
       <c r="A49" s="1">
-        <v>720104</v>
+        <v>720103</v>
       </c>
       <c r="B49" s="1">
         <v>1</v>
@@ -2410,10 +2972,10 @@
         <v>24</v>
       </c>
       <c r="D49" s="1">
-        <v>20104</v>
+        <v>20103</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>88</v>
@@ -2421,40 +2983,70 @@
       <c r="I49" s="1">
         <v>12</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="10" t="s">
         <v>31</v>
       </c>
       <c r="K49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="1">
+        <v>720104</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="1">
+        <v>20104</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I50" s="1">
+        <v>12</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" s="1">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2464,7 +3056,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -2474,7 +3066,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -2484,17 +3076,17 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -2502,7 +3094,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -2512,7 +3104,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
@@ -2522,7 +3114,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -2532,17 +3124,17 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -2550,7 +3142,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>52</v>
       </c>
@@ -2560,7 +3152,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -2570,17 +3162,17 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,7 +3182,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -2602,19 +3194,19 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -2626,7 +3218,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -2638,7 +3230,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>66</v>
       </c>
@@ -2650,29 +3242,29 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -2684,9 +3276,9 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -2696,12 +3288,12 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>70</v>
@@ -2710,12 +3302,12 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>77</v>
@@ -2724,53 +3316,54 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A5:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2785,7 +3378,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2800,13 +3393,13 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E9" s="1">
         <v>7</v>
@@ -2815,7 +3408,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2830,7 +3423,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2842,30 +3435,30 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C12" s="1"/>
       <c r="E12" s="1">
         <v>8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C13" s="1"/>
       <c r="E13" s="1">
@@ -2875,34 +3468,34 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2911,24 +3504,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2936,7 +3529,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2944,15 +3537,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2960,75 +3553,75 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="1">
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="1">
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="1">
         <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="1">
         <v>104</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="1">
         <v>105</v>
       </c>
       <c r="B32" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F36">
+  <sortState ref="E5:F36">
     <sortCondition ref="E5:E36"/>
   </sortState>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD75E053-9341-4DCD-9ECA-9A38D949B9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12345"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,18 +36,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pe</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1&gt;
@@ -56,6 +61,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -68,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="140">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -482,19 +488,20 @@
   </si>
   <si>
     <t>正义光环效果层数&gt;=1</t>
+  </si>
+  <si>
+    <t>释放动作指定id1次</t>
+  </si>
+  <si>
+    <t>释放动作指定id1次</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,180 +513,65 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -688,7 +580,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -712,186 +604,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -899,256 +617,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1156,65 +638,23 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="23" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="适中" xfId="2" builtinId="28"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1492,14 +932,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
@@ -1515,12 +955,12 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1555,7 +995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1590,7 +1030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1625,7 +1065,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1010001</v>
       </c>
@@ -1660,7 +1100,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2010002</v>
       </c>
@@ -1695,7 +1135,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3010001</v>
       </c>
@@ -1728,7 +1168,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4010003</v>
       </c>
@@ -1761,7 +1201,7 @@
         <v>55010001</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>4020101</v>
       </c>
@@ -1792,7 +1232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>5010001</v>
       </c>
@@ -1825,7 +1265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>6010102</v>
       </c>
@@ -1856,7 +1296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>7010001</v>
       </c>
@@ -1889,7 +1329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>8010006</v>
       </c>
@@ -1922,7 +1362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>9010001</v>
       </c>
@@ -1955,7 +1395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>10020004</v>
       </c>
@@ -1984,7 +1424,7 @@
       </c>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>11010007</v>
       </c>
@@ -2017,7 +1457,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>12010008</v>
       </c>
@@ -2050,7 +1490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14010009</v>
       </c>
@@ -2083,7 +1523,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15010009</v>
       </c>
@@ -2116,7 +1556,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>17010001</v>
       </c>
@@ -2149,7 +1589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>18010001</v>
       </c>
@@ -2182,7 +1622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>19010002</v>
       </c>
@@ -2215,7 +1655,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21010001</v>
       </c>
@@ -2248,7 +1688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>23010015</v>
       </c>
@@ -2281,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23020016</v>
       </c>
@@ -2312,7 +1752,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24010014</v>
       </c>
@@ -2345,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>24020016</v>
       </c>
@@ -2376,7 +1816,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24020017</v>
       </c>
@@ -2407,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>26010001</v>
       </c>
@@ -2439,7 +1879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26010002</v>
       </c>
@@ -2465,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>26010003</v>
       </c>
@@ -2491,7 +1931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>26010004</v>
       </c>
@@ -2517,7 +1957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>26010005</v>
       </c>
@@ -2543,7 +1983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>720001</v>
       </c>
@@ -2569,7 +2009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>720011</v>
       </c>
@@ -2598,7 +2038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>720022</v>
       </c>
@@ -2627,7 +2067,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>720023</v>
       </c>
@@ -2656,7 +2096,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>720053</v>
       </c>
@@ -2685,7 +2125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>720032</v>
       </c>
@@ -2711,7 +2151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>720033</v>
       </c>
@@ -2737,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>720034</v>
       </c>
@@ -2764,7 +2204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>720051</v>
       </c>
@@ -2793,7 +2233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>720052</v>
       </c>
@@ -2822,7 +2262,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>720081</v>
       </c>
@@ -2848,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>720084</v>
       </c>
@@ -2877,7 +2317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>720091</v>
       </c>
@@ -2903,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>720101</v>
       </c>
@@ -2932,7 +2372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>720102</v>
       </c>
@@ -2961,15 +2401,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>720103</v>
       </c>
       <c r="B49" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="D49" s="1">
         <v>20103</v>
@@ -2987,10 +2427,10 @@
         <v>31</v>
       </c>
       <c r="K49" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>21103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>720104</v>
       </c>
@@ -3020,23 +2460,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>105</v>
@@ -3046,7 +2485,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -3056,7 +2495,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -3066,7 +2505,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -3076,7 +2515,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>106</v>
       </c>
@@ -3086,7 +2525,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -3094,7 +2533,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -3104,7 +2543,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
@@ -3114,7 +2553,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -3124,7 +2563,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>108</v>
       </c>
@@ -3134,7 +2573,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -3142,7 +2581,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>52</v>
       </c>
@@ -3152,7 +2591,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -3162,7 +2601,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>109</v>
       </c>
@@ -3172,7 +2611,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -3182,7 +2621,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -3194,7 +2633,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
@@ -3206,7 +2645,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -3218,7 +2657,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -3230,7 +2669,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>66</v>
       </c>
@@ -3242,7 +2681,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>112</v>
       </c>
@@ -3254,7 +2693,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>114</v>
@@ -3264,7 +2703,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -3276,7 +2715,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>115</v>
       </c>
@@ -3288,7 +2727,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>116</v>
       </c>
@@ -3302,7 +2741,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
@@ -3316,7 +2755,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>119</v>
       </c>
@@ -3329,23 +2768,22 @@
       <c r="F27" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A5:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A5:F42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3354,7 +2792,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -3363,7 +2801,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3378,7 +2816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -3393,7 +2831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -3408,7 +2846,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -3423,7 +2861,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -3438,7 +2876,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -3453,7 +2891,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -3468,7 +2906,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -3477,7 +2915,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -3486,7 +2924,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -3495,7 +2933,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -3504,7 +2942,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3513,7 +2951,7 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3521,7 +2959,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3529,7 +2967,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3537,7 +2975,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3545,7 +2983,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3553,7 +2991,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3561,7 +2999,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3569,7 +3007,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3577,51 +3015,74 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
         <v>101</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B38" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="1">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>102</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B39" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="1">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
         <v>103</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B40" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
         <v>104</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B41" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="1">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
         <v>105</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B42" t="s">
         <v>137</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="E5:F36">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F36">
     <sortCondition ref="E5:E36"/>
   </sortState>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_condition_v8【迷宫-技能-自动释放条件】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD75E053-9341-4DCD-9ECA-9A38D949B9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_condition_v8" sheetId="1" r:id="rId1"/>
@@ -29,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,19 +32,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pe</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1&gt;
@@ -61,7 +56,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -74,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="140">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -385,6 +379,9 @@
     <t>攻击次数—触发火焰冲击</t>
   </si>
   <si>
+    <t>释放动作指定id1次</t>
+  </si>
+  <si>
     <t>攻击次数—触发引燃</t>
   </si>
   <si>
@@ -475,6 +472,9 @@
     <t>普攻概率触发&gt;=（万分比）</t>
   </si>
   <si>
+    <t>释放动作指定id</t>
+  </si>
+  <si>
     <t>冰冻效果层数&gt;=1</t>
   </si>
   <si>
@@ -488,20 +488,19 @@
   </si>
   <si>
     <t>正义光环效果层数&gt;=1</t>
-  </si>
-  <si>
-    <t>释放动作指定id1次</t>
-  </si>
-  <si>
-    <t>释放动作指定id1次</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,65 +512,180 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -580,7 +694,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,12 +724,186 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -617,44 +911,323 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="23" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="差" xfId="1" builtinId="27"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="适中" xfId="2" builtinId="28"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -932,14 +1505,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="40.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
@@ -955,117 +1528,117 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="9" t="s">
+      <c r="J3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>1010001</v>
       </c>
@@ -1093,14 +1666,14 @@
       <c r="I5" s="1">
         <v>12</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="K5" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>2010002</v>
       </c>
@@ -1128,14 +1701,14 @@
       <c r="I6" s="1">
         <v>12</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="9">
+      <c r="J6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="10">
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>3010001</v>
       </c>
@@ -1161,14 +1734,14 @@
       <c r="I7" s="1">
         <v>12</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="9">
+      <c r="J7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="10">
         <v>55010001</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <v>4010003</v>
       </c>
@@ -1194,14 +1767,14 @@
       <c r="I8" s="1">
         <v>12</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="9">
+      <c r="J8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="10">
         <v>55010001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11">
       <c r="A9" s="1">
         <v>4020101</v>
       </c>
@@ -1225,14 +1798,14 @@
       <c r="I9" s="1">
         <v>12</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1">
         <v>5010001</v>
       </c>
@@ -1258,14 +1831,14 @@
       <c r="I10" s="1">
         <v>12</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11">
       <c r="A11" s="1">
         <v>6010102</v>
       </c>
@@ -1289,14 +1862,14 @@
       <c r="I11" s="1">
         <v>12</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1">
         <v>7010001</v>
       </c>
@@ -1322,14 +1895,14 @@
       <c r="I12" s="1">
         <v>12</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
         <v>8010006</v>
       </c>
@@ -1355,14 +1928,14 @@
       <c r="I13" s="1">
         <v>12</v>
       </c>
-      <c r="J13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="1">
         <v>9010001</v>
       </c>
@@ -1388,14 +1961,14 @@
       <c r="I14" s="1">
         <v>12</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11">
       <c r="A15" s="1">
         <v>10020004</v>
       </c>
@@ -1419,12 +1992,12 @@
       <c r="I15" s="1">
         <v>12</v>
       </c>
-      <c r="J15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="1">
         <v>11010007</v>
       </c>
@@ -1450,14 +2023,14 @@
       <c r="I16" s="1">
         <v>12</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" s="9">
+      <c r="J16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="10">
         <v>200000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:11">
       <c r="A17" s="1">
         <v>12010008</v>
       </c>
@@ -1483,14 +2056,14 @@
       <c r="I17" s="1">
         <v>12</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1">
         <v>14010009</v>
       </c>
@@ -1516,14 +2089,14 @@
       <c r="I18" s="1">
         <v>12</v>
       </c>
-      <c r="J18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="9">
+      <c r="J18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="10">
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11">
       <c r="A19" s="1">
         <v>15010009</v>
       </c>
@@ -1549,14 +2122,14 @@
       <c r="I19" s="1">
         <v>23</v>
       </c>
-      <c r="J19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="9">
+      <c r="J19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="10">
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:11">
       <c r="A20" s="1">
         <v>17010001</v>
       </c>
@@ -1582,14 +2155,14 @@
       <c r="I20" s="1">
         <v>12</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:11">
       <c r="A21" s="1">
         <v>18010001</v>
       </c>
@@ -1615,14 +2188,14 @@
       <c r="I21" s="1">
         <v>12</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:11">
       <c r="A22" s="1">
         <v>19010002</v>
       </c>
@@ -1648,14 +2221,14 @@
       <c r="I22" s="1">
         <v>12</v>
       </c>
-      <c r="J22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="9">
+      <c r="J22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="10">
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11">
       <c r="A23" s="1">
         <v>21010001</v>
       </c>
@@ -1681,14 +2254,14 @@
       <c r="I23" s="1">
         <v>12</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:11">
       <c r="A24" s="1">
         <v>23010015</v>
       </c>
@@ -1714,14 +2287,14 @@
       <c r="I24" s="1">
         <v>12</v>
       </c>
-      <c r="J24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1">
         <v>23020016</v>
       </c>
@@ -1745,14 +2318,14 @@
       <c r="I25" s="1">
         <v>23</v>
       </c>
-      <c r="J25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" s="9">
+      <c r="J25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="10">
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:11">
       <c r="A26" s="1">
         <v>24010014</v>
       </c>
@@ -1778,14 +2351,14 @@
       <c r="I26" s="1">
         <v>12</v>
       </c>
-      <c r="J26" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="J26" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1">
         <v>24020016</v>
       </c>
@@ -1809,14 +2382,14 @@
       <c r="I27" s="1">
         <v>23</v>
       </c>
-      <c r="J27" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K27" s="9">
+      <c r="J27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="10">
         <v>600000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:11">
       <c r="A28" s="1">
         <v>24020017</v>
       </c>
@@ -1840,14 +2413,14 @@
       <c r="I28" s="1">
         <v>23</v>
       </c>
-      <c r="J28" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K28" s="9">
+      <c r="J28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:11">
       <c r="A29" s="1">
         <v>26010001</v>
       </c>
@@ -1866,20 +2439,20 @@
       <c r="F29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I29" s="1">
         <v>12</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:11">
       <c r="A30" s="1">
         <v>26010002</v>
       </c>
@@ -1892,20 +2465,20 @@
       <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I30" s="1">
         <v>12</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:11">
       <c r="A31" s="1">
         <v>26010003</v>
       </c>
@@ -1918,20 +2491,20 @@
       <c r="F31" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I31" s="1">
         <v>12</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11">
       <c r="A32" s="1">
         <v>26010004</v>
       </c>
@@ -1944,20 +2517,20 @@
       <c r="F32" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I32" s="1">
         <v>12</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>26010005</v>
       </c>
@@ -1970,20 +2543,20 @@
       <c r="F33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I33" s="1">
         <v>12</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>720001</v>
       </c>
@@ -1996,20 +2569,20 @@
       <c r="D34" s="1">
         <v>20001</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I34" s="1">
         <v>12</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>720011</v>
       </c>
@@ -2025,20 +2598,20 @@
       <c r="F35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="8" t="s">
         <v>90</v>
       </c>
       <c r="I35" s="1">
         <v>12</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:11">
       <c r="A36" s="1">
         <v>720022</v>
       </c>
@@ -2054,20 +2627,20 @@
       <c r="F36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="8" t="s">
         <v>90</v>
       </c>
       <c r="I36" s="1">
         <v>2</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K36" s="1">
         <v>20021</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11">
       <c r="A37" s="1">
         <v>720023</v>
       </c>
@@ -2083,20 +2656,20 @@
       <c r="F37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="8" t="s">
         <v>90</v>
       </c>
       <c r="I37" s="1">
         <v>2</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K37" s="1">
         <v>20021</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:11">
       <c r="A38" s="1">
         <v>720053</v>
       </c>
@@ -2112,20 +2685,20 @@
       <c r="F38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I38" s="1">
         <v>12</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K38" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:11">
       <c r="A39" s="1">
         <v>720032</v>
       </c>
@@ -2138,20 +2711,20 @@
       <c r="D39" s="1">
         <v>20032</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I39" s="1">
         <v>12</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:11">
       <c r="A40" s="1">
         <v>720033</v>
       </c>
@@ -2164,47 +2737,47 @@
       <c r="D40" s="1">
         <v>20033</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I40" s="1">
         <v>12</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:11">
       <c r="A41" s="1">
         <v>720034</v>
       </c>
       <c r="B41" s="1">
         <v>18</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D41" s="1">
         <v>20102</v>
       </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="6" t="s">
+      <c r="F41" s="9"/>
+      <c r="G41" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I41" s="1">
         <v>12</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:11">
       <c r="A42" s="1">
         <v>720051</v>
       </c>
@@ -2220,20 +2793,20 @@
       <c r="F42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I42" s="1">
         <v>12</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K42" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:11">
       <c r="A43" s="1">
         <v>720052</v>
       </c>
@@ -2249,20 +2822,20 @@
       <c r="F43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I43" s="1">
         <v>12</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="J43" s="11" t="s">
         <v>99</v>
       </c>
       <c r="K43" s="1">
         <v>2500</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:11">
       <c r="A44" s="1">
         <v>720081</v>
       </c>
@@ -2275,20 +2848,20 @@
       <c r="D44" s="1">
         <v>20081</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I44" s="1">
         <v>12</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="J44" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:11">
       <c r="A45" s="1">
         <v>720084</v>
       </c>
@@ -2304,20 +2877,20 @@
       <c r="F45" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I45" s="1">
         <v>12</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="J45" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K45" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:11">
       <c r="A46" s="1">
         <v>720091</v>
       </c>
@@ -2330,20 +2903,20 @@
       <c r="D46" s="1">
         <v>20091</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I46" s="1">
         <v>12</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K46" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:11">
       <c r="A47" s="1">
         <v>720101</v>
       </c>
@@ -2359,20 +2932,20 @@
       <c r="F47" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I47" s="1">
         <v>12</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:11">
       <c r="A48" s="1">
         <v>720102</v>
       </c>
@@ -2388,49 +2961,49 @@
       <c r="F48" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I48" s="1">
         <v>12</v>
       </c>
-      <c r="J48" s="10" t="s">
+      <c r="J48" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K48" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11">
       <c r="A49" s="1">
         <v>720103</v>
       </c>
       <c r="B49" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="D49" s="1">
         <v>20103</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G49" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I49" s="1">
         <v>12</v>
       </c>
-      <c r="J49" s="10" t="s">
+      <c r="J49" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K49" s="1">
         <v>21103</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:11">
       <c r="A50" s="1">
         <v>720104</v>
       </c>
@@ -2444,15 +3017,15 @@
         <v>20104</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G50" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G50" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I50" s="1">
         <v>12</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="J50" s="11" t="s">
         <v>31</v>
       </c>
       <c r="K50" s="1">
@@ -2460,32 +3033,33 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
     <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2495,7 +3069,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -2505,7 +3079,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -2515,17 +3089,17 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -2533,7 +3107,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -2543,7 +3117,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
@@ -2553,7 +3127,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -2563,17 +3137,17 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -2581,7 +3155,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>52</v>
       </c>
@@ -2591,7 +3165,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
@@ -2601,17 +3175,17 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -2621,7 +3195,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -2633,19 +3207,19 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -2657,7 +3231,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -2669,7 +3243,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>66</v>
       </c>
@@ -2681,29 +3255,29 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -2715,9 +3289,9 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -2727,12 +3301,12 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>70</v>
@@ -2741,12 +3315,12 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>77</v>
@@ -2755,53 +3329,54 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A5:F42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2816,7 +3391,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2831,13 +3406,13 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E9" s="1">
         <v>7</v>
@@ -2846,7 +3421,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -2861,7 +3436,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -2873,30 +3448,30 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C12" s="1"/>
       <c r="E12" s="1">
         <v>8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="1"/>
       <c r="E13" s="1">
@@ -2906,34 +3481,34 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2942,24 +3517,24 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2967,7 +3542,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2975,15 +3550,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2991,98 +3566,103 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1">
       <c r="A32" s="1"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="1">
         <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="1">
         <v>102</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="1">
         <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="1">
         <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="1">
         <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E5:F36">
+  <sortState ref="E5:F36">
     <sortCondition ref="E5:E36"/>
   </sortState>
-  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>